--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/23.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/23.xlsx
@@ -426,13 +426,13 @@
         <v>-11.05755727016365</v>
       </c>
       <c r="E2">
-        <v>-11.66089520724615</v>
+        <v>-8.81994914545573</v>
       </c>
       <c r="F2">
-        <v>3.777135692156496</v>
+        <v>3.581264906294942</v>
       </c>
       <c r="G2">
-        <v>-18.34466914809819</v>
+        <v>-18.66786758012736</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-10.44033589692105</v>
       </c>
       <c r="E3">
-        <v>-11.06917888337517</v>
+        <v>-10.05356089242425</v>
       </c>
       <c r="F3">
-        <v>3.907123105003794</v>
+        <v>3.629272110756784</v>
       </c>
       <c r="G3">
-        <v>-17.66160046014079</v>
+        <v>-18.0065855557828</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-9.64546697273269</v>
       </c>
       <c r="E4">
-        <v>-11.17430081521791</v>
+        <v>-10.79640842319441</v>
       </c>
       <c r="F4">
-        <v>3.521277852453813</v>
+        <v>3.327340476110392</v>
       </c>
       <c r="G4">
-        <v>-17.20445516611997</v>
+        <v>-17.8137167991143</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-8.780892559112376</v>
       </c>
       <c r="E5">
-        <v>-11.60869349410438</v>
+        <v>-11.10647472107213</v>
       </c>
       <c r="F5">
-        <v>4.371500900808781</v>
+        <v>3.286680890511382</v>
       </c>
       <c r="G5">
-        <v>-16.38021829663188</v>
+        <v>-16.88406589527084</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-7.866936983076779</v>
       </c>
       <c r="E6">
-        <v>-12.52227123601559</v>
+        <v>-11.40247409219266</v>
       </c>
       <c r="F6">
-        <v>4.185391596421815</v>
+        <v>3.613475144385398</v>
       </c>
       <c r="G6">
-        <v>-15.5837153669352</v>
+        <v>-15.97541843166288</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-6.965152115918084</v>
       </c>
       <c r="E7">
-        <v>-14.09956952653632</v>
+        <v>-12.68222801698003</v>
       </c>
       <c r="F7">
-        <v>3.971392818317397</v>
+        <v>3.756703181799043</v>
       </c>
       <c r="G7">
-        <v>-15.29408588885857</v>
+        <v>-15.62221601742035</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-6.106534838756082</v>
       </c>
       <c r="E8">
-        <v>-14.43940188997909</v>
+        <v>-13.29734353345509</v>
       </c>
       <c r="F8">
-        <v>3.722392203975088</v>
+        <v>3.733238846747345</v>
       </c>
       <c r="G8">
-        <v>-14.13767745818167</v>
+        <v>-15.07943699543872</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-5.326814321029067</v>
       </c>
       <c r="E9">
-        <v>-14.15789722638221</v>
+        <v>-13.86077648820398</v>
       </c>
       <c r="F9">
-        <v>4.366953163767411</v>
+        <v>3.593158605464337</v>
       </c>
       <c r="G9">
-        <v>-15.02072396032917</v>
+        <v>-14.58014514611125</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-4.646057828060519</v>
       </c>
       <c r="E10">
-        <v>-16.04870482696895</v>
+        <v>-14.18287463928973</v>
       </c>
       <c r="F10">
-        <v>4.414264539610902</v>
+        <v>3.763076640596183</v>
       </c>
       <c r="G10">
-        <v>-13.85325249944743</v>
+        <v>-13.92011888991502</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-4.071556076230928</v>
       </c>
       <c r="E11">
-        <v>-14.99162117415094</v>
+        <v>-14.95843286245424</v>
       </c>
       <c r="F11">
-        <v>4.373086396017738</v>
+        <v>4.35867943014825</v>
       </c>
       <c r="G11">
-        <v>-13.00366529997964</v>
+        <v>-13.41151320925876</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-3.610153316201266</v>
       </c>
       <c r="E12">
-        <v>-17.23541435844619</v>
+        <v>-15.37387859127684</v>
       </c>
       <c r="F12">
-        <v>4.982150155865297</v>
+        <v>4.592254186715627</v>
       </c>
       <c r="G12">
-        <v>-12.04640316134056</v>
+        <v>-12.89599819304212</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-3.244153722629963</v>
       </c>
       <c r="E13">
-        <v>-18.0743713524842</v>
+        <v>-16.22298188058141</v>
       </c>
       <c r="F13">
-        <v>5.582878882905888</v>
+        <v>4.56823153203444</v>
       </c>
       <c r="G13">
-        <v>-12.23188090007161</v>
+        <v>-12.46626049573881</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-2.968727466439667</v>
       </c>
       <c r="E14">
-        <v>-17.50034355564567</v>
+        <v>-16.4884966805777</v>
       </c>
       <c r="F14">
-        <v>5.482050002637132</v>
+        <v>4.510414800788646</v>
       </c>
       <c r="G14">
-        <v>-11.11015882203224</v>
+        <v>-12.04445424050329</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-2.755026192212386</v>
       </c>
       <c r="E15">
-        <v>-19.60848870486069</v>
+        <v>-18.22242087658037</v>
       </c>
       <c r="F15">
-        <v>5.241437436615571</v>
+        <v>4.726911934979908</v>
       </c>
       <c r="G15">
-        <v>-11.62933279679333</v>
+        <v>-11.81822538944956</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-2.588006919713486</v>
       </c>
       <c r="E16">
-        <v>-19.95637829827363</v>
+        <v>-18.8120398287323</v>
       </c>
       <c r="F16">
-        <v>5.482260407957443</v>
+        <v>5.091590743653557</v>
       </c>
       <c r="G16">
-        <v>-10.29019443606752</v>
+        <v>-11.34580854494302</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-2.440252351145845</v>
       </c>
       <c r="E17">
-        <v>-19.95338798611975</v>
+        <v>-19.22720729239613</v>
       </c>
       <c r="F17">
-        <v>5.979598942719822</v>
+        <v>5.382528286129994</v>
       </c>
       <c r="G17">
-        <v>-10.33942133070526</v>
+        <v>-11.4904398791738</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-2.295507762629677</v>
       </c>
       <c r="E18">
-        <v>-19.86354571874107</v>
+        <v>-20.58487546163729</v>
       </c>
       <c r="F18">
-        <v>5.87542180140895</v>
+        <v>5.387170457055282</v>
       </c>
       <c r="G18">
-        <v>-9.907768652244359</v>
+        <v>-10.80094353803308</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-2.137768919355666</v>
       </c>
       <c r="E19">
-        <v>-22.36498752078337</v>
+        <v>-22.27289421286662</v>
       </c>
       <c r="F19">
-        <v>6.315024784931008</v>
+        <v>5.624323760802753</v>
       </c>
       <c r="G19">
-        <v>-9.652646690800768</v>
+        <v>-10.34270042591169</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-1.958767140063168</v>
       </c>
       <c r="E20">
-        <v>-23.08517513056526</v>
+        <v>-22.05413211275393</v>
       </c>
       <c r="F20">
-        <v>6.347960672866317</v>
+        <v>5.781902435102497</v>
       </c>
       <c r="G20">
-        <v>-9.723134184016237</v>
+        <v>-10.86531144592698</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-1.755217877887191</v>
       </c>
       <c r="E21">
-        <v>-22.40166037678161</v>
+        <v>-22.69429564672902</v>
       </c>
       <c r="F21">
-        <v>6.595455315270336</v>
+        <v>5.930998627197575</v>
       </c>
       <c r="G21">
-        <v>-9.688248109417485</v>
+        <v>-9.709431691029778</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-1.526133576162204</v>
       </c>
       <c r="E22">
-        <v>-23.91119071811512</v>
+        <v>-23.26445265061281</v>
       </c>
       <c r="F22">
-        <v>6.327967197232348</v>
+        <v>5.984009170772326</v>
       </c>
       <c r="G22">
-        <v>-9.811441314438348</v>
+        <v>-9.674520814357411</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-1.276396958493605</v>
       </c>
       <c r="E23">
-        <v>-25.11309269661857</v>
+        <v>-23.50538043956612</v>
       </c>
       <c r="F23">
-        <v>7.053628639228354</v>
+        <v>5.725934619899752</v>
       </c>
       <c r="G23">
-        <v>-9.728905234934892</v>
+        <v>-9.373005921529739</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-1.009787425828412</v>
       </c>
       <c r="E24">
-        <v>-25.02438010272023</v>
+        <v>-24.35177998829823</v>
       </c>
       <c r="F24">
-        <v>6.868417285106024</v>
+        <v>6.096045862000959</v>
       </c>
       <c r="G24">
-        <v>-8.125620874086312</v>
+        <v>-9.356006058124704</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-0.7352365135458974</v>
       </c>
       <c r="E25">
-        <v>-25.55719558358249</v>
+        <v>-25.1323511375318</v>
       </c>
       <c r="F25">
-        <v>6.353128028724981</v>
+        <v>5.700750594119841</v>
       </c>
       <c r="G25">
-        <v>-8.673083571864405</v>
+        <v>-9.232619658004099</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-0.458330732460078</v>
       </c>
       <c r="E26">
-        <v>-25.10295055456334</v>
+        <v>-25.23503513432686</v>
       </c>
       <c r="F26">
-        <v>6.960811728479475</v>
+        <v>5.567527578197208</v>
       </c>
       <c r="G26">
-        <v>-8.660236097731536</v>
+        <v>-9.290448956069554</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-0.1864953892908055</v>
       </c>
       <c r="E27">
-        <v>-25.2141486345743</v>
+        <v>-25.46350328930568</v>
       </c>
       <c r="F27">
-        <v>6.324983417847464</v>
+        <v>6.092528614008672</v>
       </c>
       <c r="G27">
-        <v>-8.987951117903327</v>
+        <v>-8.491471040500494</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>0.07500116821528804</v>
       </c>
       <c r="E28">
-        <v>-26.40004413663187</v>
+        <v>-26.43443272640145</v>
       </c>
       <c r="F28">
-        <v>6.310718931171257</v>
+        <v>5.612749811450838</v>
       </c>
       <c r="G28">
-        <v>-7.898102315204563</v>
+        <v>-8.405778570786383</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>0.3196614786041231</v>
       </c>
       <c r="E29">
-        <v>-26.34151292943106</v>
+        <v>-26.89591680275977</v>
       </c>
       <c r="F29">
-        <v>6.204686246878114</v>
+        <v>5.416415139843716</v>
       </c>
       <c r="G29">
-        <v>-7.538288190285034</v>
+        <v>-8.301898348878282</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>0.5418676801718763</v>
       </c>
       <c r="E30">
-        <v>-26.40804737485481</v>
+        <v>-26.89357854478389</v>
       </c>
       <c r="F30">
-        <v>6.217192937925581</v>
+        <v>5.370642870634627</v>
       </c>
       <c r="G30">
-        <v>-7.742693827301658</v>
+        <v>-7.742342682154153</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>0.7353249455296441</v>
       </c>
       <c r="E31">
-        <v>-26.07399212836487</v>
+        <v>-27.7260606823665</v>
       </c>
       <c r="F31">
-        <v>6.08422505916301</v>
+        <v>5.185529263865827</v>
       </c>
       <c r="G31">
-        <v>-8.112035864606455</v>
+        <v>-7.37463888708028</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>0.8952355596747275</v>
       </c>
       <c r="E32">
-        <v>-26.54062203355466</v>
+        <v>-27.21717185194658</v>
       </c>
       <c r="F32">
-        <v>6.172472695318048</v>
+        <v>5.124029611147185</v>
       </c>
       <c r="G32">
-        <v>-7.691993167342238</v>
+        <v>-7.103032684288401</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>1.018590597506877</v>
       </c>
       <c r="E33">
-        <v>-26.28155301753451</v>
+        <v>-28.15933822401225</v>
       </c>
       <c r="F33">
-        <v>6.759937603505012</v>
+        <v>5.206243419140231</v>
       </c>
       <c r="G33">
-        <v>-6.954930365123726</v>
+        <v>-7.558202950026047</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>1.10177693394069</v>
       </c>
       <c r="E34">
-        <v>-27.56168073134111</v>
+        <v>-27.70925263613492</v>
       </c>
       <c r="F34">
-        <v>5.637739999258494</v>
+        <v>5.397788470424366</v>
       </c>
       <c r="G34">
-        <v>-8.203896218417071</v>
+        <v>-7.00524202413907</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>1.143393919101586</v>
       </c>
       <c r="E35">
-        <v>-24.70237747549495</v>
+        <v>-27.16244083310799</v>
       </c>
       <c r="F35">
-        <v>5.779170479408064</v>
+        <v>5.546921110685167</v>
       </c>
       <c r="G35">
-        <v>-6.831852032864872</v>
+        <v>-6.839229997079359</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>1.140269412678118</v>
       </c>
       <c r="E36">
-        <v>-25.49213137496772</v>
+        <v>-26.63682702068299</v>
       </c>
       <c r="F36">
-        <v>6.15399181856159</v>
+        <v>5.550948632997578</v>
       </c>
       <c r="G36">
-        <v>-6.689091297133616</v>
+        <v>-6.758464002408678</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>1.091710276543593</v>
       </c>
       <c r="E37">
-        <v>-25.22540799047591</v>
+        <v>-26.78587331549711</v>
       </c>
       <c r="F37">
-        <v>6.072273374275419</v>
+        <v>5.368240605166508</v>
       </c>
       <c r="G37">
-        <v>-8.095616891872943</v>
+        <v>-6.675283068991217</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>0.9953986967623566</v>
       </c>
       <c r="E38">
-        <v>-24.46609713001413</v>
+        <v>-26.97189565073618</v>
       </c>
       <c r="F38">
-        <v>6.41902465561768</v>
+        <v>5.469982346313149</v>
       </c>
       <c r="G38">
-        <v>-7.352554598584053</v>
+        <v>-6.976852787455305</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>0.8535380503944382</v>
       </c>
       <c r="E39">
-        <v>-25.28819208607334</v>
+        <v>-27.23880592973761</v>
       </c>
       <c r="F39">
-        <v>7.057690952971683</v>
+        <v>5.786728503591207</v>
       </c>
       <c r="G39">
-        <v>-7.377964975689358</v>
+        <v>-6.852236726632285</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>0.6680377146680859</v>
       </c>
       <c r="E40">
-        <v>-24.00766981719088</v>
+        <v>-26.07472309355805</v>
       </c>
       <c r="F40">
-        <v>6.532560691845381</v>
+        <v>5.919437931724104</v>
       </c>
       <c r="G40">
-        <v>-7.357781309255461</v>
+        <v>-6.7474701569355</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>0.4437277117254561</v>
       </c>
       <c r="E41">
-        <v>-23.67136353016289</v>
+        <v>-25.79027795634319</v>
       </c>
       <c r="F41">
-        <v>7.133088953974494</v>
+        <v>6.304400144622702</v>
       </c>
       <c r="G41">
-        <v>-7.757039868829826</v>
+        <v>-7.230901732871947</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>0.1853031253010136</v>
       </c>
       <c r="E42">
-        <v>-23.1109084279339</v>
+        <v>-25.96953471033411</v>
       </c>
       <c r="F42">
-        <v>7.204900124123183</v>
+        <v>6.392210402789061</v>
       </c>
       <c r="G42">
-        <v>-7.453540810112906</v>
+        <v>-6.886560185771652</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-0.1020974295348047</v>
       </c>
       <c r="E43">
-        <v>-23.70757537970407</v>
+        <v>-26.00309681105005</v>
       </c>
       <c r="F43">
-        <v>6.424826540906889</v>
+        <v>6.542661803955118</v>
       </c>
       <c r="G43">
-        <v>-7.978806957377352</v>
+        <v>-7.580477822877425</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-0.412125873007855</v>
       </c>
       <c r="E44">
-        <v>-21.15964668330296</v>
+        <v>-25.36878515183164</v>
       </c>
       <c r="F44">
-        <v>7.257819547283627</v>
+        <v>6.338451015082178</v>
       </c>
       <c r="G44">
-        <v>-7.220247284195614</v>
+        <v>-7.871775566747776</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-0.7397640820829225</v>
       </c>
       <c r="E45">
-        <v>-23.41432543448058</v>
+        <v>-24.10610923201197</v>
       </c>
       <c r="F45">
-        <v>6.967700431801156</v>
+        <v>6.808054152464024</v>
       </c>
       <c r="G45">
-        <v>-8.565271568602085</v>
+        <v>-7.918028823296235</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-1.077956593075294</v>
       </c>
       <c r="E46">
-        <v>-22.81394966499733</v>
+        <v>-24.20951588757755</v>
       </c>
       <c r="F46">
-        <v>7.250813215790749</v>
+        <v>6.576316714796056</v>
       </c>
       <c r="G46">
-        <v>-8.52338608775456</v>
+        <v>-8.218678254291955</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-1.423037401871334</v>
       </c>
       <c r="E47">
-        <v>-22.31087533043218</v>
+        <v>-23.26547434059872</v>
       </c>
       <c r="F47">
-        <v>6.927849332787277</v>
+        <v>7.169654747868869</v>
       </c>
       <c r="G47">
-        <v>-8.958958799219014</v>
+        <v>-8.209430996950232</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-1.767179689932896</v>
       </c>
       <c r="E48">
-        <v>-20.63731390782457</v>
+        <v>-23.2424198645346</v>
       </c>
       <c r="F48">
-        <v>7.016670199185051</v>
+        <v>6.888361058695825</v>
       </c>
       <c r="G48">
-        <v>-9.659741389227118</v>
+        <v>-8.68063776133879</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-2.107904411521448</v>
       </c>
       <c r="E49">
-        <v>-20.74267257271282</v>
+        <v>-22.40281912274123</v>
       </c>
       <c r="F49">
-        <v>7.100466188917443</v>
+        <v>7.077570113904065</v>
       </c>
       <c r="G49">
-        <v>-9.032135359363327</v>
+        <v>-8.321968447922465</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-2.437385822969019</v>
       </c>
       <c r="E50">
-        <v>-20.5269340104446</v>
+        <v>-22.70889833774712</v>
       </c>
       <c r="F50">
-        <v>6.712429076219655</v>
+        <v>7.178831401957082</v>
       </c>
       <c r="G50">
-        <v>-9.33536028989818</v>
+        <v>-8.909729293836685</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-2.753190295766949</v>
       </c>
       <c r="E51">
-        <v>-18.58695238777189</v>
+        <v>-22.50834391608248</v>
       </c>
       <c r="F51">
-        <v>7.334904104318538</v>
+        <v>7.029147069006018</v>
       </c>
       <c r="G51">
-        <v>-8.778136018093916</v>
+        <v>-9.009237823926968</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-3.049918415925021</v>
       </c>
       <c r="E52">
-        <v>-18.70038074226428</v>
+        <v>-21.64539382022093</v>
       </c>
       <c r="F52">
-        <v>7.143529696719379</v>
+        <v>7.26439844119666</v>
       </c>
       <c r="G52">
-        <v>-10.45338555359653</v>
+        <v>-9.195299064074135</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-3.325065832151954</v>
       </c>
       <c r="E53">
-        <v>-20.78813777708572</v>
+        <v>-21.45253529914119</v>
       </c>
       <c r="F53">
-        <v>6.617238064494352</v>
+        <v>6.999347380057708</v>
       </c>
       <c r="G53">
-        <v>-10.59362300468048</v>
+        <v>-9.906899274295519</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-3.576569746171174</v>
       </c>
       <c r="E54">
-        <v>-18.66081309797264</v>
+        <v>-20.78404686393076</v>
       </c>
       <c r="F54">
-        <v>6.780023856288095</v>
+        <v>7.275414070919088</v>
       </c>
       <c r="G54">
-        <v>-10.1178670178419</v>
+        <v>-9.882807323208725</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-3.802708478291198</v>
       </c>
       <c r="E55">
-        <v>-18.65438808005313</v>
+        <v>-20.68889263926761</v>
       </c>
       <c r="F55">
-        <v>7.13641070725972</v>
+        <v>7.453648914775041</v>
       </c>
       <c r="G55">
-        <v>-9.849671752858315</v>
+        <v>-9.510628711905683</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-4.006017343737372</v>
       </c>
       <c r="E56">
-        <v>-17.11632933012938</v>
+        <v>-19.70370522769371</v>
       </c>
       <c r="F56">
-        <v>7.123362263930822</v>
+        <v>7.017889556001972</v>
       </c>
       <c r="G56">
-        <v>-9.955301173642463</v>
+        <v>-9.896328369446101</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-4.184674957301364</v>
       </c>
       <c r="E57">
-        <v>-18.28344816378739</v>
+        <v>-19.93872299693178</v>
       </c>
       <c r="F57">
-        <v>6.935089263887745</v>
+        <v>7.239269087665335</v>
       </c>
       <c r="G57">
-        <v>-10.65432151105157</v>
+        <v>-10.17713222543247</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-4.345043137798744</v>
       </c>
       <c r="E58">
-        <v>-17.92095172614503</v>
+        <v>-19.47314385420718</v>
       </c>
       <c r="F58">
-        <v>7.621603719162252</v>
+        <v>7.409331258725268</v>
       </c>
       <c r="G58">
-        <v>-11.54714525169278</v>
+        <v>-10.74287274609295</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-4.484152431631082</v>
       </c>
       <c r="E59">
-        <v>-16.67154946971952</v>
+        <v>-18.6465551234945</v>
       </c>
       <c r="F59">
-        <v>7.130257594191725</v>
+        <v>7.581858651175931</v>
       </c>
       <c r="G59">
-        <v>-10.20458159406344</v>
+        <v>-10.4187592480846</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-4.610177784017067</v>
       </c>
       <c r="E60">
-        <v>-16.93496274478544</v>
+        <v>-18.60154261915601</v>
       </c>
       <c r="F60">
-        <v>7.375548779304298</v>
+        <v>7.727025068312128</v>
       </c>
       <c r="G60">
-        <v>-10.75709086113615</v>
+        <v>-10.68320939995224</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-4.719628893458172</v>
       </c>
       <c r="E61">
-        <v>-16.80987217289293</v>
+        <v>-17.62096111894135</v>
       </c>
       <c r="F61">
-        <v>7.626699835424274</v>
+        <v>7.578914633426383</v>
       </c>
       <c r="G61">
-        <v>-10.8307856540818</v>
+        <v>-10.63269279748649</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-4.819479743599328</v>
       </c>
       <c r="E62">
-        <v>-15.9905515619987</v>
+        <v>-18.49301090081559</v>
       </c>
       <c r="F62">
-        <v>7.299092124760709</v>
+        <v>7.421458557502252</v>
       </c>
       <c r="G62">
-        <v>-11.1913151230193</v>
+        <v>-10.75640684605328</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-4.908109572973382</v>
       </c>
       <c r="E63">
-        <v>-15.54153957924884</v>
+        <v>-17.91408646782509</v>
       </c>
       <c r="F63">
-        <v>6.986507685314316</v>
+        <v>7.691726676544036</v>
       </c>
       <c r="G63">
-        <v>-10.85823110659588</v>
+        <v>-10.55666660962098</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-4.98930486031399</v>
       </c>
       <c r="E64">
-        <v>-15.34358922108486</v>
+        <v>-17.38421561379214</v>
       </c>
       <c r="F64">
-        <v>7.527143327486218</v>
+        <v>7.392715865359915</v>
       </c>
       <c r="G64">
-        <v>-11.34245895963262</v>
+        <v>-11.22378756424356</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-5.064098399083856</v>
       </c>
       <c r="E65">
-        <v>-14.92568063794664</v>
+        <v>-17.5923828718152</v>
       </c>
       <c r="F65">
-        <v>6.844349898585087</v>
+        <v>7.588530322238078</v>
       </c>
       <c r="G65">
-        <v>-11.04170901497014</v>
+        <v>-11.12776698892701</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-5.132348358934512</v>
       </c>
       <c r="E66">
-        <v>-15.19360845372265</v>
+        <v>-16.86913849849823</v>
       </c>
       <c r="F66">
-        <v>6.67123270854363</v>
+        <v>7.641575657243748</v>
       </c>
       <c r="G66">
-        <v>-10.6682955214755</v>
+        <v>-10.85181389639092</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-5.198895313131583</v>
       </c>
       <c r="E67">
-        <v>-16.17790707807304</v>
+        <v>-17.06264492054465</v>
       </c>
       <c r="F67">
-        <v>7.734788527611165</v>
+        <v>7.610503595964738</v>
       </c>
       <c r="G67">
-        <v>-11.05593104613023</v>
+        <v>-11.44521525599424</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-5.260130498780656</v>
       </c>
       <c r="E68">
-        <v>-15.23585491931881</v>
+        <v>-17.6917110738598</v>
       </c>
       <c r="F68">
-        <v>7.030258738060574</v>
+        <v>7.542575812200374</v>
       </c>
       <c r="G68">
-        <v>-11.42566077900681</v>
+        <v>-11.28416103291306</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-5.324226770715053</v>
       </c>
       <c r="E69">
-        <v>-14.58012514929826</v>
+        <v>-16.72398376269548</v>
       </c>
       <c r="F69">
-        <v>6.766957188876335</v>
+        <v>7.695984484994425</v>
       </c>
       <c r="G69">
-        <v>-11.43949380922282</v>
+        <v>-11.4379116980006</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-5.384710488065569</v>
       </c>
       <c r="E70">
-        <v>-15.71584155212924</v>
+        <v>-16.13483827663457</v>
       </c>
       <c r="F70">
-        <v>7.365533817404452</v>
+        <v>7.950694207476828</v>
       </c>
       <c r="G70">
-        <v>-10.76201603080729</v>
+        <v>-10.76926606853681</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-5.451381763187819</v>
       </c>
       <c r="E71">
-        <v>-14.80965237316491</v>
+        <v>-16.98773760109004</v>
       </c>
       <c r="F71">
-        <v>7.491879727149044</v>
+        <v>7.804836931926697</v>
       </c>
       <c r="G71">
-        <v>-10.4446121463981</v>
+        <v>-11.72969373499261</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-5.516614292144223</v>
       </c>
       <c r="E72">
-        <v>-15.75165054017192</v>
+        <v>-15.8920083168945</v>
       </c>
       <c r="F72">
-        <v>7.400908418973602</v>
+        <v>7.915314635703261</v>
       </c>
       <c r="G72">
-        <v>-11.35184458643767</v>
+        <v>-11.21213189501654</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-5.587890968755633</v>
       </c>
       <c r="E73">
-        <v>-15.00695898357353</v>
+        <v>-16.88897008257429</v>
       </c>
       <c r="F73">
-        <v>7.231434388769657</v>
+        <v>7.721224839757726</v>
       </c>
       <c r="G73">
-        <v>-10.60974696327519</v>
+        <v>-11.44631699021169</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-5.659805997960051</v>
       </c>
       <c r="E74">
-        <v>-16.40742184230572</v>
+        <v>-16.11337863371918</v>
       </c>
       <c r="F74">
-        <v>7.086615885942636</v>
+        <v>7.603979374300289</v>
       </c>
       <c r="G74">
-        <v>-11.53647513854891</v>
+        <v>-11.37289763082041</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-5.734932017661635</v>
       </c>
       <c r="E75">
-        <v>-15.91188973950645</v>
+        <v>-16.18914151470671</v>
       </c>
       <c r="F75">
-        <v>6.403588857433915</v>
+        <v>7.782060141819322</v>
       </c>
       <c r="G75">
-        <v>-11.21934668769408</v>
+        <v>-11.57277623671604</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-5.812112891503089</v>
       </c>
       <c r="E76">
-        <v>-16.65571742814927</v>
+        <v>-16.67104693114921</v>
       </c>
       <c r="F76">
-        <v>6.729572967987993</v>
+        <v>7.612158674035532</v>
       </c>
       <c r="G76">
-        <v>-11.96605619117675</v>
+        <v>-11.52570712248286</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-5.88942438149902</v>
       </c>
       <c r="E77">
-        <v>-16.02469926551144</v>
+        <v>-17.81275641792193</v>
       </c>
       <c r="F77">
-        <v>6.652060973373238</v>
+        <v>7.544060246586191</v>
       </c>
       <c r="G77">
-        <v>-10.42095096816884</v>
+        <v>-11.1726587421712</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-5.969754152573068</v>
       </c>
       <c r="E78">
-        <v>-16.69217847036994</v>
+        <v>-17.9407168588399</v>
       </c>
       <c r="F78">
-        <v>6.7601115606596</v>
+        <v>7.666096989101419</v>
       </c>
       <c r="G78">
-        <v>-10.63226594074584</v>
+        <v>-10.66061601626074</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-6.046725459709585</v>
       </c>
       <c r="E79">
-        <v>-18.18741761153471</v>
+        <v>-17.98432973096192</v>
       </c>
       <c r="F79">
-        <v>6.654937064995758</v>
+        <v>7.610758733124801</v>
       </c>
       <c r="G79">
-        <v>-10.63728118110537</v>
+        <v>-10.91649248289116</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-6.127344736352185</v>
       </c>
       <c r="E80">
-        <v>-17.16738060373417</v>
+        <v>-17.84327421473677</v>
       </c>
       <c r="F80">
-        <v>7.160559273786131</v>
+        <v>7.594544269582403</v>
       </c>
       <c r="G80">
-        <v>-10.39397544968116</v>
+        <v>-10.57229974823256</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-6.201922084394735</v>
       </c>
       <c r="E81">
-        <v>-17.40756496786033</v>
+        <v>-19.0414590691045</v>
       </c>
       <c r="F81">
-        <v>7.03711927689056</v>
+        <v>7.51954222819813</v>
       </c>
       <c r="G81">
-        <v>-10.55251552572111</v>
+        <v>-10.15110310185907</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-6.279675677164529</v>
       </c>
       <c r="E82">
-        <v>-19.81991208056241</v>
+        <v>-19.91761637697901</v>
       </c>
       <c r="F82">
-        <v>6.700447570105562</v>
+        <v>7.724370979153559</v>
       </c>
       <c r="G82">
-        <v>-10.36321043541948</v>
+        <v>-10.43066163267548</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-6.350112794592106</v>
       </c>
       <c r="E83">
-        <v>-19.70839835649077</v>
+        <v>-20.41059840802483</v>
       </c>
       <c r="F83">
-        <v>6.436200025347325</v>
+        <v>7.55441649585599</v>
       </c>
       <c r="G83">
-        <v>-9.506990639317968</v>
+        <v>-10.33942002533296</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-6.420396193198371</v>
       </c>
       <c r="E84">
-        <v>-21.06044723080943</v>
+        <v>-21.95778591644056</v>
       </c>
       <c r="F84">
-        <v>6.890410439650351</v>
+        <v>7.521309964235704</v>
       </c>
       <c r="G84">
-        <v>-8.440788655753213</v>
+        <v>-10.01069334163211</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-6.48314711253863</v>
       </c>
       <c r="E85">
-        <v>-22.2636242451896</v>
+        <v>-22.18884152207474</v>
       </c>
       <c r="F85">
-        <v>7.204633389819482</v>
+        <v>7.884524219341204</v>
       </c>
       <c r="G85">
-        <v>-10.15913766833822</v>
+        <v>-9.840462351313162</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-6.540495522727316</v>
       </c>
       <c r="E86">
-        <v>-23.17437365018861</v>
+        <v>-23.39993455724004</v>
       </c>
       <c r="F86">
-        <v>6.701933661226184</v>
+        <v>7.851573420792645</v>
       </c>
       <c r="G86">
-        <v>-9.974701616699026</v>
+        <v>-10.2247156563501</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-6.58873829731959</v>
       </c>
       <c r="E87">
-        <v>-24.66147665036804</v>
+        <v>-24.50897073052034</v>
       </c>
       <c r="F87">
-        <v>6.751120460869614</v>
+        <v>7.475887266070597</v>
       </c>
       <c r="G87">
-        <v>-10.63256356562923</v>
+        <v>-9.989341366993694</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-6.623835218332869</v>
       </c>
       <c r="E88">
-        <v>-25.64889433642337</v>
+        <v>-26.03004284612554</v>
       </c>
       <c r="F88">
-        <v>6.598296615461939</v>
+        <v>7.887176651764968</v>
       </c>
       <c r="G88">
-        <v>-8.698095810419565</v>
+        <v>-9.901142582472113</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-6.643700214390036</v>
       </c>
       <c r="E89">
-        <v>-26.05624545637388</v>
+        <v>-26.66327882361082</v>
       </c>
       <c r="F89">
-        <v>7.077369648992588</v>
+        <v>7.608063225596092</v>
       </c>
       <c r="G89">
-        <v>-8.714882898140424</v>
+        <v>-9.827814599141515</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-6.636693293139158</v>
       </c>
       <c r="E90">
-        <v>-29.75212591616893</v>
+        <v>-29.68762654429434</v>
       </c>
       <c r="F90">
-        <v>7.15968286107397</v>
+        <v>7.916633396608519</v>
       </c>
       <c r="G90">
-        <v>-8.783751729709401</v>
+        <v>-9.14041338053516</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-6.601169405914604</v>
       </c>
       <c r="E91">
-        <v>-30.34982494095332</v>
+        <v>-30.68868337634042</v>
       </c>
       <c r="F91">
-        <v>7.251106457851339</v>
+        <v>7.975710903041374</v>
       </c>
       <c r="G91">
-        <v>-8.582505093648024</v>
+        <v>-9.351556043969151</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-6.520950426844172</v>
       </c>
       <c r="E92">
-        <v>-31.35738154872275</v>
+        <v>-32.30182595720008</v>
       </c>
       <c r="F92">
-        <v>6.105918344707524</v>
+        <v>7.680010247998839</v>
       </c>
       <c r="G92">
-        <v>-8.590850338733517</v>
+        <v>-9.746787530011723</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-6.397003472380405</v>
       </c>
       <c r="E93">
-        <v>-34.69710337135712</v>
+        <v>-34.38353176312124</v>
       </c>
       <c r="F93">
-        <v>6.577953568783989</v>
+        <v>7.533182125852627</v>
       </c>
       <c r="G93">
-        <v>-9.10440468576223</v>
+        <v>-9.523767284060462</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-6.216590331508937</v>
       </c>
       <c r="E94">
-        <v>-35.75548282610848</v>
+        <v>-36.48627566100832</v>
       </c>
       <c r="F94">
-        <v>6.363300380431358</v>
+        <v>7.416872715560354</v>
       </c>
       <c r="G94">
-        <v>-9.710699207528764</v>
+        <v>-9.187059554144581</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-5.98482651458009</v>
       </c>
       <c r="E95">
-        <v>-37.60006518464988</v>
+        <v>-39.43373705704096</v>
       </c>
       <c r="F95">
-        <v>6.323757434091321</v>
+        <v>7.585019701185015</v>
       </c>
       <c r="G95">
-        <v>-8.549514419622421</v>
+        <v>-9.494269786297767</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-5.695851827392838</v>
       </c>
       <c r="E96">
-        <v>-41.60655185979488</v>
+        <v>-40.23342959121404</v>
       </c>
       <c r="F96">
-        <v>6.096884169812593</v>
+        <v>7.558666020632351</v>
       </c>
       <c r="G96">
-        <v>-8.192911510549962</v>
+        <v>-9.427289828440461</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-5.361170088218647</v>
       </c>
       <c r="E97">
-        <v>-41.24356741982185</v>
+        <v>-44.05410989810886</v>
       </c>
       <c r="F97">
-        <v>5.961389770471483</v>
+        <v>7.180945395569027</v>
       </c>
       <c r="G97">
-        <v>-7.832384652357059</v>
+        <v>-9.075464581969738</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-4.982290614771656</v>
       </c>
       <c r="E98">
-        <v>-45.00866529955649</v>
+        <v>-46.09682327950686</v>
       </c>
       <c r="F98">
-        <v>6.002518212020478</v>
+        <v>7.046582546100142</v>
       </c>
       <c r="G98">
-        <v>-7.458764910039724</v>
+        <v>-9.614649914021706</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-4.579891811719137</v>
       </c>
       <c r="E99">
-        <v>-48.4081902503599</v>
+        <v>-47.8613524897622</v>
       </c>
       <c r="F99">
-        <v>5.683810480732591</v>
+        <v>7.190892431341843</v>
       </c>
       <c r="G99">
-        <v>-8.859348450089676</v>
+        <v>-9.328119389774727</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-4.159207448861896</v>
       </c>
       <c r="E100">
-        <v>-50.37554880378305</v>
+        <v>-50.04178739699435</v>
       </c>
       <c r="F100">
-        <v>5.749881064779879</v>
+        <v>6.465633575903598</v>
       </c>
       <c r="G100">
-        <v>-7.514684448436779</v>
+        <v>-8.934304232672835</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-3.758255096620587</v>
       </c>
       <c r="E101">
-        <v>-52.80021018806325</v>
+        <v>-53.10566330646193</v>
       </c>
       <c r="F101">
-        <v>5.550650420732571</v>
+        <v>6.284310578370008</v>
       </c>
       <c r="G101">
-        <v>-9.221145435526156</v>
+        <v>-9.38137205257196</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-3.369737876013394</v>
       </c>
       <c r="E102">
-        <v>-55.06349698886299</v>
+        <v>-55.80034261011736</v>
       </c>
       <c r="F102">
-        <v>4.485795721577445</v>
+        <v>6.196594754087569</v>
       </c>
       <c r="G102">
-        <v>-8.222231477680459</v>
+        <v>-9.422249786007317</v>
       </c>
     </row>
   </sheetData>
